--- a/data/raw/Subproceso-Proceso-Area.xlsx
+++ b/data/raw/Subproceso-Proceso-Area.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/lxisilva_poligran_edu_co/Documents/Documentos/Proyectos/Sistema_Indicadores_Poli/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="421" documentId="13_ncr:1_{7D5D2E2B-8870-4A5C-A9AF-FD632C2BB311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD0FC282-F7D4-4E70-8154-F2AF5A617FA6}"/>
+  <xr:revisionPtr revIDLastSave="424" documentId="13_ncr:1_{7D5D2E2B-8870-4A5C-A9AF-FD632C2BB311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE829267-DEF5-47E2-A0C5-50CD66F71819}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7C8BB491-4D7A-4ED1-AB08-0ADDFA03A5A0}"/>
   </bookViews>
@@ -26,12 +26,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Hoja1!$A$1:$G$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Hoja1 (2)'!$A$1:$H$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Hoja2!$A$1:$D$54</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Proceso!$B$1:$D$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Proceso!$A$1:$D$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Rectoria!$A$1:$F$60</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId9"/>
+    <pivotCache cacheId="2" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1598,7 +1598,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{692C4F03-8B8F-4909-A847-49A10CEFB19B}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{692C4F03-8B8F-4909-A847-49A10CEFB19B}" name="TablaDinámica1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:B44" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="6">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -2943,6 +2943,7 @@
     <cfRule type="duplicateValues" dxfId="6" priority="11"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8256,6 +8257,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004B3553A73F55864994CAF6806DB2233B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0772d54a1d010170e6fbd4301e22082d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="787dcc16-ad9c-4aed-8595-d8b714944830" xmlns:ns3="eb4e1f33-0654-4877-a695-74ac1243131b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d309db89fd7fb813f1d992ce290f04b6" ns2:_="" ns3:_="">
     <xsd:import namespace="787dcc16-ad9c-4aed-8595-d8b714944830"/>
@@ -8490,27 +8511,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE277362-6D14-47AE-9D5E-D8EAD6BC850B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50A7858D-C4BB-4738-AFE6-ACA2D8E7AA74}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
+    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D12D41D8-D34A-4C1F-82E4-8461693B79B3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8527,23 +8547,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50A7858D-C4BB-4738-AFE6-ACA2D8E7AA74}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
-    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE277362-6D14-47AE-9D5E-D8EAD6BC850B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/raw/Subproceso-Proceso-Area.xlsx
+++ b/data/raw/Subproceso-Proceso-Area.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/lxisilva_poligran_edu_co/Documents/Documentos/Proyectos/Sistema_Indicadores_Poli/data/raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="424" documentId="13_ncr:1_{7D5D2E2B-8870-4A5C-A9AF-FD632C2BB311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE829267-DEF5-47E2-A0C5-50CD66F71819}"/>
+  <xr:revisionPtr revIDLastSave="427" documentId="13_ncr:1_{7D5D2E2B-8870-4A5C-A9AF-FD632C2BB311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{111378DA-9568-48F8-A326-072E06712C53}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7C8BB491-4D7A-4ED1-AB08-0ADDFA03A5A0}"/>
   </bookViews>
@@ -31,7 +31,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId9"/>
+    <pivotCache cacheId="1" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1598,7 +1598,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{692C4F03-8B8F-4909-A847-49A10CEFB19B}" name="TablaDinámica1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{692C4F03-8B8F-4909-A847-49A10CEFB19B}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:B44" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="6">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -8257,26 +8257,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004B3553A73F55864994CAF6806DB2233B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0772d54a1d010170e6fbd4301e22082d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="787dcc16-ad9c-4aed-8595-d8b714944830" xmlns:ns3="eb4e1f33-0654-4877-a695-74ac1243131b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d309db89fd7fb813f1d992ce290f04b6" ns2:_="" ns3:_="">
     <xsd:import namespace="787dcc16-ad9c-4aed-8595-d8b714944830"/>
@@ -8511,10 +8491,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE277362-6D14-47AE-9D5E-D8EAD6BC850B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D12D41D8-D34A-4C1F-82E4-8461693B79B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
+    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -8531,20 +8542,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D12D41D8-D34A-4C1F-82E4-8461693B79B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE277362-6D14-47AE-9D5E-D8EAD6BC850B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
-    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>